--- a/AAII_Financials/Yearly/SNY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SNY_YR_FIN.xlsx
@@ -2471,7 +2471,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>8045100</v>
+        <v>8047400</v>
       </c>
       <c r="E47" s="3">
         <v>3374100</v>
@@ -2726,7 +2726,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1089600</v>
+        <v>1087200</v>
       </c>
       <c r="E52" s="3">
         <v>898600</v>
@@ -3023,7 +3023,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>16496400</v>
+        <v>16323800</v>
       </c>
       <c r="E59" s="3">
         <v>15289400</v>
@@ -3125,7 +3125,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>18451300</v>
+        <v>18546400</v>
       </c>
       <c r="E61" s="3">
         <v>13910300</v>
@@ -3176,7 +3176,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>9308400</v>
+        <v>9213300</v>
       </c>
       <c r="E62" s="3">
         <v>8474000</v>
